--- a/ai/119_261021_main_cate_reclassify/scripts/CaseTypeQA.xlsx
+++ b/ai/119_261021_main_cate_reclassify/scripts/CaseTypeQA.xlsx
@@ -18391,7 +18391,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>必問</t>
+          <t>條件式必問</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21338,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>現場有沒有其他人受傷？</t>
+          <t>現場有沒有其他人受傷？幾個人受傷？</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>必問</t>
+          <t>條件式必問</t>
         </is>
       </c>
     </row>
